--- a/input/timetable/Экономика.xlsx
+++ b/input/timetable/Экономика.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="167">
   <si>
     <t>пара</t>
   </si>
@@ -369,9 +369,6 @@
     <t>Финансы общественного сектора (пр), К603</t>
   </si>
   <si>
-    <t>Эконометрика (пр), К612</t>
-  </si>
-  <si>
     <t>Бухгалтерский финансовый учет (пр), К612</t>
   </si>
   <si>
@@ -471,9 +468,6 @@
     <t>Бюджет и бюджетная система РФ (лек), К612</t>
   </si>
   <si>
-    <t>Актуарные расчеты (пр), К609</t>
-  </si>
-  <si>
     <t>Анализ финансовой отчетности (лек), К608</t>
   </si>
   <si>
@@ -531,10 +525,13 @@
     <t>Экономико-математические методы и модели (пр), ЭОиДОТ</t>
   </si>
   <si>
-    <t>Эконометрика (пр), К526</t>
-  </si>
-  <si>
-    <t>Международные стандарты финансовой отчетности (пр), К526</t>
+    <t>Актуарные расчеты (пр), К612</t>
+  </si>
+  <si>
+    <t>Эконометрика (пр), К609</t>
+  </si>
+  <si>
+    <t>Международные стандарты финансовой отчетности (пр), К609</t>
   </si>
 </sst>
 </file>
@@ -1764,169 +1761,85 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1946,6 +1859,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1965,86 +1881,151 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2065,36 +2046,82 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2103,6 +2130,115 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2112,6 +2248,30 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2136,27 +2296,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2166,253 +2308,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2429,6 +2324,108 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2928,21 +2925,21 @@
       <c r="A8" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="188" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
+      <c r="D8" s="188"/>
+      <c r="E8" s="188"/>
+      <c r="F8" s="188"/>
       <c r="G8" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="144" t="s">
+      <c r="I8" s="188" t="s">
         <v>87</v>
       </c>
-      <c r="J8" s="144"/>
-      <c r="K8" s="144"/>
-      <c r="L8" s="144"/>
+      <c r="J8" s="188"/>
+      <c r="K8" s="188"/>
+      <c r="L8" s="188"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="49" t="s">
@@ -2977,108 +2974,108 @@
       <c r="B10" s="2">
         <v>1</v>
       </c>
-      <c r="C10" s="153"/>
-      <c r="D10" s="154"/>
-      <c r="E10" s="154"/>
-      <c r="F10" s="155"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="199"/>
+      <c r="E10" s="199"/>
+      <c r="F10" s="200"/>
       <c r="G10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="114">
         <v>1</v>
       </c>
-      <c r="I10" s="153"/>
-      <c r="J10" s="154"/>
-      <c r="K10" s="154"/>
-      <c r="L10" s="155"/>
+      <c r="I10" s="198"/>
+      <c r="J10" s="199"/>
+      <c r="K10" s="199"/>
+      <c r="L10" s="200"/>
     </row>
     <row r="11" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="6">
         <v>2</v>
       </c>
-      <c r="C11" s="138" t="s">
+      <c r="C11" s="157" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="140"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="149"/>
       <c r="G11" s="7"/>
       <c r="H11" s="115">
         <v>2</v>
       </c>
-      <c r="I11" s="138" t="s">
+      <c r="I11" s="157" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="139"/>
-      <c r="K11" s="139"/>
-      <c r="L11" s="140"/>
+      <c r="J11" s="166"/>
+      <c r="K11" s="166"/>
+      <c r="L11" s="149"/>
     </row>
     <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="6">
         <v>3</v>
       </c>
-      <c r="C12" s="138" t="s">
+      <c r="C12" s="157" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="140"/>
+      <c r="D12" s="166"/>
+      <c r="E12" s="166"/>
+      <c r="F12" s="149"/>
       <c r="G12" s="7"/>
       <c r="H12" s="115">
         <v>3</v>
       </c>
-      <c r="I12" s="138" t="s">
+      <c r="I12" s="157" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="139"/>
-      <c r="K12" s="139"/>
-      <c r="L12" s="140"/>
+      <c r="J12" s="166"/>
+      <c r="K12" s="166"/>
+      <c r="L12" s="149"/>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="6">
         <v>4</v>
       </c>
-      <c r="C13" s="156" t="s">
+      <c r="C13" s="120" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="157"/>
-      <c r="E13" s="157"/>
-      <c r="F13" s="158"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="150"/>
       <c r="G13" s="8"/>
       <c r="H13" s="116">
         <v>4</v>
       </c>
-      <c r="I13" s="138" t="s">
+      <c r="I13" s="157" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="139"/>
-      <c r="K13" s="139"/>
-      <c r="L13" s="140"/>
+      <c r="J13" s="166"/>
+      <c r="K13" s="166"/>
+      <c r="L13" s="149"/>
     </row>
     <row r="14" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="9"/>
       <c r="B14" s="10">
         <v>5</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="201" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="122"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="203"/>
       <c r="G14" s="11"/>
       <c r="H14" s="31">
         <v>5</v>
       </c>
-      <c r="I14" s="120" t="s">
+      <c r="I14" s="201" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="121"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="122"/>
+      <c r="J14" s="202"/>
+      <c r="K14" s="202"/>
+      <c r="L14" s="203"/>
     </row>
     <row r="15" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
@@ -3087,110 +3084,110 @@
       <c r="B15" s="14">
         <v>1</v>
       </c>
-      <c r="C15" s="126"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="128" t="s">
+      <c r="C15" s="136"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="193" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="129"/>
+      <c r="F15" s="194"/>
       <c r="G15" s="13" t="s">
         <v>22</v>
       </c>
       <c r="H15" s="117">
         <v>1</v>
       </c>
-      <c r="I15" s="180" t="s">
+      <c r="I15" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="J15" s="181"/>
-      <c r="K15" s="181"/>
-      <c r="L15" s="182"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="143"/>
+      <c r="L15" s="144"/>
     </row>
     <row r="16" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="190" t="s">
+      <c r="C16" s="154" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="191"/>
-      <c r="E16" s="191"/>
-      <c r="F16" s="192"/>
+      <c r="D16" s="155"/>
+      <c r="E16" s="155"/>
+      <c r="F16" s="156"/>
       <c r="G16" s="8"/>
       <c r="H16" s="116">
         <v>2</v>
       </c>
-      <c r="I16" s="156" t="s">
+      <c r="I16" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="157"/>
-      <c r="K16" s="157" t="s">
+      <c r="J16" s="121"/>
+      <c r="K16" s="121" t="s">
         <v>44</v>
       </c>
-      <c r="L16" s="158"/>
+      <c r="L16" s="150"/>
     </row>
     <row r="17" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8"/>
       <c r="B17" s="15">
         <v>3</v>
       </c>
-      <c r="C17" s="156" t="s">
+      <c r="C17" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="157"/>
-      <c r="E17" s="157"/>
-      <c r="F17" s="158"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="150"/>
       <c r="G17" s="8"/>
       <c r="H17" s="116">
         <v>3</v>
       </c>
-      <c r="I17" s="138"/>
-      <c r="J17" s="193"/>
-      <c r="K17" s="186" t="s">
+      <c r="I17" s="157"/>
+      <c r="J17" s="158"/>
+      <c r="K17" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="L17" s="140"/>
+      <c r="L17" s="149"/>
     </row>
     <row r="18" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="119"/>
       <c r="B18" s="17">
         <v>4</v>
       </c>
-      <c r="C18" s="197" t="s">
+      <c r="C18" s="162" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="198"/>
-      <c r="E18" s="199"/>
-      <c r="F18" s="200"/>
+      <c r="D18" s="163"/>
+      <c r="E18" s="164"/>
+      <c r="F18" s="165"/>
       <c r="G18" s="119"/>
       <c r="H18" s="118"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="139"/>
-      <c r="L18" s="140"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="166"/>
+      <c r="K18" s="166"/>
+      <c r="L18" s="149"/>
     </row>
     <row r="19" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16"/>
       <c r="B19" s="12">
         <v>7</v>
       </c>
-      <c r="C19" s="141" t="s">
-        <v>165</v>
-      </c>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="143"/>
+      <c r="C19" s="205" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" s="206"/>
+      <c r="E19" s="206"/>
+      <c r="F19" s="207"/>
       <c r="G19" s="16"/>
       <c r="H19" s="31">
         <v>8</v>
       </c>
-      <c r="I19" s="194" t="s">
-        <v>165</v>
-      </c>
-      <c r="J19" s="195"/>
-      <c r="K19" s="195"/>
-      <c r="L19" s="196"/>
+      <c r="I19" s="159" t="s">
+        <v>163</v>
+      </c>
+      <c r="J19" s="160"/>
+      <c r="K19" s="160"/>
+      <c r="L19" s="161"/>
     </row>
     <row r="20" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
@@ -3199,72 +3196,72 @@
       <c r="B20" s="14">
         <v>1</v>
       </c>
-      <c r="C20" s="168" t="s">
+      <c r="C20" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="169"/>
-      <c r="E20" s="169"/>
-      <c r="F20" s="170"/>
+      <c r="D20" s="146"/>
+      <c r="E20" s="146"/>
+      <c r="F20" s="147"/>
       <c r="G20" s="13" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="117">
         <v>1</v>
       </c>
-      <c r="I20" s="187"/>
-      <c r="J20" s="188"/>
-      <c r="K20" s="188"/>
-      <c r="L20" s="189"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="152"/>
+      <c r="K20" s="152"/>
+      <c r="L20" s="153"/>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
       <c r="B21" s="15"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="132"/>
+      <c r="C21" s="204"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="123"/>
       <c r="G21" s="8"/>
       <c r="H21" s="116">
         <v>2</v>
       </c>
-      <c r="I21" s="156" t="s">
-        <v>150</v>
-      </c>
-      <c r="J21" s="157"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="132"/>
+      <c r="I21" s="120" t="s">
+        <v>148</v>
+      </c>
+      <c r="J21" s="121"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="123"/>
     </row>
     <row r="22" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8"/>
       <c r="B22" s="15"/>
-      <c r="C22" s="130"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="132"/>
+      <c r="C22" s="204"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="123"/>
       <c r="G22" s="8"/>
       <c r="H22" s="116">
         <v>3</v>
       </c>
-      <c r="I22" s="174" t="s">
+      <c r="I22" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="J22" s="175"/>
-      <c r="K22" s="175"/>
-      <c r="L22" s="176"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="132"/>
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16"/>
       <c r="B23" s="12"/>
-      <c r="C23" s="201"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="202"/>
-      <c r="F23" s="203"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="129"/>
       <c r="G23" s="16"/>
       <c r="H23" s="31"/>
-      <c r="I23" s="204"/>
-      <c r="J23" s="205"/>
-      <c r="K23" s="205"/>
-      <c r="L23" s="206"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="134"/>
+      <c r="L23" s="135"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
@@ -3273,108 +3270,108 @@
       <c r="B24" s="14">
         <v>1</v>
       </c>
-      <c r="C24" s="126"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="207"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="138"/>
       <c r="G24" s="13" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="14">
         <v>1</v>
       </c>
-      <c r="I24" s="150"/>
-      <c r="J24" s="151"/>
-      <c r="K24" s="151"/>
-      <c r="L24" s="152"/>
+      <c r="I24" s="195"/>
+      <c r="J24" s="196"/>
+      <c r="K24" s="196"/>
+      <c r="L24" s="197"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8"/>
       <c r="B25" s="15">
         <v>2</v>
       </c>
-      <c r="C25" s="149" t="s">
+      <c r="C25" s="139" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="124"/>
-      <c r="E25" s="124"/>
-      <c r="F25" s="125"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="141"/>
       <c r="G25" s="8"/>
       <c r="H25" s="15">
         <v>2</v>
       </c>
-      <c r="I25" s="149" t="s">
+      <c r="I25" s="139" t="s">
         <v>62</v>
       </c>
-      <c r="J25" s="124"/>
-      <c r="K25" s="124"/>
-      <c r="L25" s="125"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="140"/>
+      <c r="L25" s="141"/>
     </row>
     <row r="26" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>
       <c r="B26" s="15">
         <v>3</v>
       </c>
-      <c r="C26" s="123" t="s">
+      <c r="C26" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="133"/>
-      <c r="E26" s="133" t="s">
-        <v>125</v>
-      </c>
-      <c r="F26" s="134"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" s="126"/>
       <c r="G26" s="8"/>
       <c r="H26" s="15">
         <v>3</v>
       </c>
-      <c r="I26" s="138" t="s">
+      <c r="I26" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="J26" s="139"/>
-      <c r="K26" s="139"/>
-      <c r="L26" s="140"/>
+      <c r="J26" s="166"/>
+      <c r="K26" s="166"/>
+      <c r="L26" s="149"/>
     </row>
     <row r="27" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8"/>
       <c r="B27" s="15">
         <v>4</v>
       </c>
-      <c r="C27" s="123" t="s">
+      <c r="C27" s="124" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="133"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="134"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="126"/>
       <c r="G27" s="8"/>
       <c r="H27" s="15">
         <v>4</v>
       </c>
-      <c r="I27" s="123" t="s">
+      <c r="I27" s="124" t="s">
         <v>93</v>
       </c>
-      <c r="J27" s="133"/>
-      <c r="K27" s="133"/>
-      <c r="L27" s="134"/>
+      <c r="J27" s="125"/>
+      <c r="K27" s="125"/>
+      <c r="L27" s="126"/>
     </row>
     <row r="28" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16"/>
       <c r="B28" s="12">
         <v>5</v>
       </c>
-      <c r="C28" s="171"/>
-      <c r="D28" s="172"/>
-      <c r="E28" s="172"/>
-      <c r="F28" s="173"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="176"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="177"/>
       <c r="G28" s="16"/>
       <c r="H28" s="12">
         <v>5</v>
       </c>
-      <c r="I28" s="163" t="s">
+      <c r="I28" s="170" t="s">
         <v>98</v>
       </c>
-      <c r="J28" s="166"/>
-      <c r="K28" s="166"/>
-      <c r="L28" s="167"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="174"/>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
@@ -3383,90 +3380,90 @@
       <c r="B29" s="4">
         <v>1</v>
       </c>
-      <c r="C29" s="168" t="s">
+      <c r="C29" s="145" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="169"/>
-      <c r="E29" s="169"/>
-      <c r="F29" s="170"/>
+      <c r="D29" s="146"/>
+      <c r="E29" s="146"/>
+      <c r="F29" s="147"/>
       <c r="G29" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H29" s="117">
         <v>1</v>
       </c>
-      <c r="I29" s="148" t="s">
+      <c r="I29" s="192" t="s">
         <v>92</v>
       </c>
-      <c r="J29" s="128"/>
-      <c r="K29" s="128"/>
-      <c r="L29" s="129"/>
+      <c r="J29" s="193"/>
+      <c r="K29" s="193"/>
+      <c r="L29" s="194"/>
     </row>
     <row r="30" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18"/>
       <c r="B30" s="15">
         <v>2</v>
       </c>
-      <c r="C30" s="145" t="s">
+      <c r="C30" s="189" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="146"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="147"/>
+      <c r="D30" s="190"/>
+      <c r="E30" s="190"/>
+      <c r="F30" s="191"/>
       <c r="G30" s="18"/>
       <c r="H30" s="116">
         <v>2</v>
       </c>
-      <c r="I30" s="123" t="s">
+      <c r="I30" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="133"/>
-      <c r="K30" s="133"/>
-      <c r="L30" s="134"/>
+      <c r="J30" s="125"/>
+      <c r="K30" s="125"/>
+      <c r="L30" s="126"/>
     </row>
     <row r="31" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="18"/>
       <c r="B31" s="15">
         <v>3</v>
       </c>
-      <c r="C31" s="138" t="s">
+      <c r="C31" s="157" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="140"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="149"/>
       <c r="G31" s="18"/>
       <c r="H31" s="116">
         <v>3</v>
       </c>
-      <c r="I31" s="174" t="s">
+      <c r="I31" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
-      <c r="L31" s="176"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="131"/>
+      <c r="L31" s="132"/>
     </row>
     <row r="32" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19"/>
       <c r="B32" s="12">
         <v>4</v>
       </c>
-      <c r="C32" s="163" t="s">
+      <c r="C32" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="166"/>
-      <c r="E32" s="166"/>
-      <c r="F32" s="167"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="173"/>
+      <c r="F32" s="174"/>
       <c r="G32" s="19"/>
       <c r="H32" s="31">
         <v>5</v>
       </c>
-      <c r="I32" s="138" t="s">
+      <c r="I32" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="J32" s="139"/>
-      <c r="K32" s="139"/>
-      <c r="L32" s="140"/>
+      <c r="J32" s="166"/>
+      <c r="K32" s="166"/>
+      <c r="L32" s="149"/>
     </row>
     <row r="33" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20" t="s">
@@ -3475,73 +3472,73 @@
       <c r="B33" s="14">
         <v>1</v>
       </c>
-      <c r="C33" s="135" t="s">
+      <c r="C33" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="136"/>
-      <c r="E33" s="136"/>
-      <c r="F33" s="137"/>
+      <c r="D33" s="168"/>
+      <c r="E33" s="168"/>
+      <c r="F33" s="169"/>
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="117">
         <v>2</v>
       </c>
-      <c r="I33" s="135" t="s">
+      <c r="I33" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="J33" s="136"/>
-      <c r="K33" s="136"/>
-      <c r="L33" s="137"/>
+      <c r="J33" s="168"/>
+      <c r="K33" s="168"/>
+      <c r="L33" s="169"/>
     </row>
     <row r="34" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="15">
         <v>2</v>
       </c>
-      <c r="C34" s="123"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="134"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="125"/>
+      <c r="E34" s="125"/>
+      <c r="F34" s="126"/>
       <c r="G34" s="21"/>
       <c r="H34" s="116">
         <v>3</v>
       </c>
-      <c r="I34" s="123"/>
-      <c r="J34" s="133"/>
-      <c r="K34" s="133"/>
-      <c r="L34" s="134"/>
+      <c r="I34" s="124"/>
+      <c r="J34" s="125"/>
+      <c r="K34" s="125"/>
+      <c r="L34" s="126"/>
     </row>
     <row r="35" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="23"/>
       <c r="B35" s="12">
         <v>3</v>
       </c>
-      <c r="C35" s="177"/>
-      <c r="D35" s="178"/>
-      <c r="E35" s="178"/>
-      <c r="F35" s="179"/>
+      <c r="C35" s="179"/>
+      <c r="D35" s="180"/>
+      <c r="E35" s="180"/>
+      <c r="F35" s="181"/>
       <c r="G35" s="23"/>
       <c r="H35" s="31">
         <v>4</v>
       </c>
-      <c r="I35" s="160"/>
-      <c r="J35" s="161"/>
-      <c r="K35" s="161"/>
-      <c r="L35" s="162"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="186"/>
+      <c r="K35" s="186"/>
+      <c r="L35" s="187"/>
     </row>
     <row r="36" spans="1:12" s="60" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="32"/>
       <c r="B36" s="33"/>
-      <c r="C36" s="159"/>
-      <c r="D36" s="159"/>
-      <c r="E36" s="159"/>
-      <c r="F36" s="159"/>
+      <c r="C36" s="178"/>
+      <c r="D36" s="178"/>
+      <c r="E36" s="178"/>
+      <c r="F36" s="178"/>
       <c r="G36" s="33"/>
-      <c r="H36" s="159"/>
-      <c r="I36" s="159"/>
-      <c r="J36" s="159"/>
-      <c r="K36" s="159"/>
+      <c r="H36" s="178"/>
+      <c r="I36" s="178"/>
+      <c r="J36" s="178"/>
+      <c r="K36" s="178"/>
       <c r="L36" s="59"/>
     </row>
     <row r="37" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3549,88 +3546,88 @@
       <c r="B37" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="180" t="s">
+      <c r="C37" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="181"/>
-      <c r="E37" s="181"/>
-      <c r="F37" s="182"/>
+      <c r="D37" s="143"/>
+      <c r="E37" s="143"/>
+      <c r="F37" s="144"/>
       <c r="G37" s="30"/>
       <c r="H37" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="183" t="s">
+      <c r="I37" s="182" t="s">
         <v>36</v>
       </c>
-      <c r="J37" s="184"/>
-      <c r="K37" s="184"/>
-      <c r="L37" s="185"/>
+      <c r="J37" s="183"/>
+      <c r="K37" s="183"/>
+      <c r="L37" s="184"/>
     </row>
     <row r="38" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="21"/>
       <c r="B38" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="123" t="s">
+      <c r="C38" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="D38" s="124"/>
-      <c r="E38" s="124"/>
-      <c r="F38" s="125"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="140"/>
+      <c r="F38" s="141"/>
       <c r="G38" s="21"/>
       <c r="H38" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="I38" s="123" t="s">
+      <c r="I38" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="J38" s="124"/>
-      <c r="K38" s="124"/>
-      <c r="L38" s="125"/>
+      <c r="J38" s="140"/>
+      <c r="K38" s="140"/>
+      <c r="L38" s="141"/>
     </row>
     <row r="39" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="22"/>
       <c r="B39" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="138" t="s">
+      <c r="C39" s="157" t="s">
         <v>63</v>
       </c>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="140"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="149"/>
       <c r="G39" s="22"/>
       <c r="H39" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="I39" s="138" t="s">
+      <c r="I39" s="157" t="s">
         <v>63</v>
       </c>
-      <c r="J39" s="139"/>
-      <c r="K39" s="139"/>
-      <c r="L39" s="140"/>
+      <c r="J39" s="166"/>
+      <c r="K39" s="166"/>
+      <c r="L39" s="149"/>
     </row>
     <row r="40" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="23"/>
       <c r="B40" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="163" t="s">
+      <c r="C40" s="170" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="164"/>
-      <c r="E40" s="164"/>
-      <c r="F40" s="165"/>
+      <c r="D40" s="171"/>
+      <c r="E40" s="171"/>
+      <c r="F40" s="172"/>
       <c r="G40" s="23"/>
       <c r="H40" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="163" t="s">
+      <c r="I40" s="170" t="s">
         <v>37</v>
       </c>
-      <c r="J40" s="164"/>
-      <c r="K40" s="164"/>
-      <c r="L40" s="165"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="171"/>
+      <c r="L40" s="172"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="35" t="s">
@@ -3662,28 +3659,38 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I35:L35"/>
     <mergeCell ref="I33:L33"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="I40:L40"/>
@@ -3700,38 +3707,28 @@
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="I37:L37"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6"/>
@@ -3939,20 +3936,20 @@
       <c r="A8" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="208" t="s">
+      <c r="C8" s="251" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="208"/>
-      <c r="E8" s="208"/>
+      <c r="D8" s="251"/>
+      <c r="E8" s="251"/>
       <c r="G8" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="209" t="s">
+      <c r="I8" s="252" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="209"/>
-      <c r="K8" s="209"/>
-      <c r="L8" s="209"/>
+      <c r="J8" s="252"/>
+      <c r="K8" s="252"/>
+      <c r="L8" s="252"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="49" t="s">
@@ -3987,82 +3984,82 @@
       <c r="B10" s="4">
         <v>1</v>
       </c>
-      <c r="C10" s="210" t="s">
+      <c r="C10" s="228" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="211"/>
-      <c r="E10" s="211"/>
-      <c r="F10" s="212"/>
+      <c r="D10" s="229"/>
+      <c r="E10" s="229"/>
+      <c r="F10" s="230"/>
       <c r="G10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="4">
         <v>1</v>
       </c>
-      <c r="I10" s="210" t="s">
+      <c r="I10" s="228" t="s">
         <v>101</v>
       </c>
-      <c r="J10" s="211"/>
-      <c r="K10" s="211"/>
-      <c r="L10" s="212"/>
+      <c r="J10" s="229"/>
+      <c r="K10" s="229"/>
+      <c r="L10" s="230"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="15">
         <v>2</v>
       </c>
-      <c r="C11" s="197" t="s">
+      <c r="C11" s="162" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="216"/>
-      <c r="E11" s="216"/>
-      <c r="F11" s="200"/>
+      <c r="D11" s="208"/>
+      <c r="E11" s="208"/>
+      <c r="F11" s="165"/>
       <c r="G11" s="8"/>
       <c r="H11" s="15">
         <v>2</v>
       </c>
-      <c r="I11" s="197" t="s">
-        <v>166</v>
-      </c>
-      <c r="J11" s="216"/>
-      <c r="K11" s="216"/>
-      <c r="L11" s="200"/>
+      <c r="I11" s="162" t="s">
+        <v>165</v>
+      </c>
+      <c r="J11" s="208"/>
+      <c r="K11" s="208"/>
+      <c r="L11" s="165"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="15">
         <v>3</v>
       </c>
-      <c r="C12" s="174" t="s">
+      <c r="C12" s="130" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="175"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="176"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="132"/>
       <c r="G12" s="8"/>
       <c r="H12" s="15">
         <v>3</v>
       </c>
-      <c r="I12" s="174" t="s">
+      <c r="I12" s="130" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="175"/>
-      <c r="K12" s="175"/>
-      <c r="L12" s="176"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="132"/>
     </row>
     <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="11"/>
       <c r="B13" s="12"/>
-      <c r="C13" s="220"/>
-      <c r="D13" s="221"/>
-      <c r="E13" s="221"/>
-      <c r="F13" s="222"/>
+      <c r="C13" s="259"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="261"/>
       <c r="G13" s="11"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="217"/>
-      <c r="J13" s="218"/>
-      <c r="K13" s="218"/>
-      <c r="L13" s="219"/>
+      <c r="I13" s="256"/>
+      <c r="J13" s="257"/>
+      <c r="K13" s="257"/>
+      <c r="L13" s="258"/>
     </row>
     <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
@@ -4071,106 +4068,106 @@
       <c r="B14" s="14">
         <v>1</v>
       </c>
-      <c r="C14" s="213"/>
-      <c r="D14" s="214"/>
-      <c r="E14" s="214"/>
-      <c r="F14" s="215"/>
+      <c r="C14" s="253"/>
+      <c r="D14" s="254"/>
+      <c r="E14" s="254"/>
+      <c r="F14" s="255"/>
       <c r="G14" s="13" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="14">
         <v>1</v>
       </c>
-      <c r="I14" s="213"/>
-      <c r="J14" s="214"/>
-      <c r="K14" s="214"/>
-      <c r="L14" s="215"/>
+      <c r="I14" s="253"/>
+      <c r="J14" s="254"/>
+      <c r="K14" s="254"/>
+      <c r="L14" s="255"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="8"/>
       <c r="B15" s="15">
         <v>2</v>
       </c>
-      <c r="C15" s="156"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
-      <c r="F15" s="158"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="150"/>
       <c r="G15" s="8"/>
       <c r="H15" s="15">
         <v>2</v>
       </c>
-      <c r="I15" s="240" t="s">
+      <c r="I15" s="238" t="s">
         <v>104</v>
       </c>
-      <c r="J15" s="241"/>
-      <c r="K15" s="241"/>
-      <c r="L15" s="242"/>
+      <c r="J15" s="239"/>
+      <c r="K15" s="239"/>
+      <c r="L15" s="240"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
       <c r="B16" s="15">
         <v>3</v>
       </c>
-      <c r="C16" s="197" t="s">
+      <c r="C16" s="162" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="198"/>
-      <c r="E16" s="199" t="s">
+      <c r="D16" s="163"/>
+      <c r="E16" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="200"/>
+      <c r="F16" s="165"/>
       <c r="G16" s="8"/>
       <c r="H16" s="15">
         <v>3</v>
       </c>
-      <c r="I16" s="233" t="s">
+      <c r="I16" s="231" t="s">
         <v>50</v>
       </c>
-      <c r="J16" s="246"/>
-      <c r="K16" s="246"/>
-      <c r="L16" s="236"/>
+      <c r="J16" s="244"/>
+      <c r="K16" s="244"/>
+      <c r="L16" s="234"/>
     </row>
     <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
-      <c r="C17" s="197" t="s">
+      <c r="C17" s="162" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="216"/>
-      <c r="E17" s="216"/>
-      <c r="F17" s="200"/>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208"/>
+      <c r="F17" s="165"/>
       <c r="G17" s="8"/>
       <c r="H17" s="15">
         <v>4</v>
       </c>
-      <c r="I17" s="197" t="s">
+      <c r="I17" s="162" t="s">
         <v>103</v>
       </c>
-      <c r="J17" s="216"/>
-      <c r="K17" s="216"/>
-      <c r="L17" s="200"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
+      <c r="L17" s="165"/>
     </row>
     <row r="18" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16"/>
       <c r="B18" s="12">
         <v>5</v>
       </c>
-      <c r="C18" s="177"/>
-      <c r="D18" s="178"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="179"/>
+      <c r="C18" s="179"/>
+      <c r="D18" s="180"/>
+      <c r="E18" s="180"/>
+      <c r="F18" s="181"/>
       <c r="G18" s="16"/>
       <c r="H18" s="12">
         <v>5</v>
       </c>
-      <c r="I18" s="243" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="245"/>
+      <c r="I18" s="241" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18" s="242"/>
+      <c r="K18" s="242"/>
+      <c r="L18" s="243"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
@@ -4179,108 +4176,108 @@
       <c r="B19" s="14">
         <v>1</v>
       </c>
-      <c r="C19" s="135" t="s">
+      <c r="C19" s="167" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="137"/>
+      <c r="D19" s="168"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="169"/>
       <c r="G19" s="13" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="14">
         <v>1</v>
       </c>
-      <c r="I19" s="259" t="s">
+      <c r="I19" s="209" t="s">
         <v>107</v>
       </c>
-      <c r="J19" s="260"/>
-      <c r="K19" s="260"/>
-      <c r="L19" s="261"/>
+      <c r="J19" s="210"/>
+      <c r="K19" s="210"/>
+      <c r="L19" s="211"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8"/>
       <c r="B20" s="15">
         <v>2</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="134"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="126"/>
       <c r="G20" s="8"/>
       <c r="H20" s="15">
         <v>2</v>
       </c>
-      <c r="I20" s="123" t="s">
+      <c r="I20" s="124" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="133"/>
-      <c r="K20" s="133"/>
-      <c r="L20" s="134"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="125"/>
+      <c r="L20" s="126"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
       <c r="B21" s="15">
         <v>3</v>
       </c>
-      <c r="C21" s="123" t="s">
+      <c r="C21" s="124" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="134"/>
+      <c r="D21" s="125"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="126"/>
       <c r="G21" s="8"/>
       <c r="H21" s="15">
         <v>3</v>
       </c>
-      <c r="I21" s="123" t="s">
+      <c r="I21" s="124" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="134"/>
+      <c r="J21" s="125"/>
+      <c r="K21" s="125"/>
+      <c r="L21" s="126"/>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8"/>
       <c r="B22" s="15">
         <v>4</v>
       </c>
-      <c r="C22" s="123" t="s">
+      <c r="C22" s="124" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="134"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="126"/>
       <c r="G22" s="8"/>
       <c r="H22" s="15">
         <v>4</v>
       </c>
-      <c r="I22" s="240" t="s">
+      <c r="I22" s="238" t="s">
         <v>110</v>
       </c>
-      <c r="J22" s="241"/>
-      <c r="K22" s="241"/>
-      <c r="L22" s="242"/>
+      <c r="J22" s="239"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="240"/>
     </row>
     <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16"/>
       <c r="B23" s="12">
         <v>5</v>
       </c>
-      <c r="C23" s="177"/>
-      <c r="D23" s="178"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="179"/>
+      <c r="C23" s="179"/>
+      <c r="D23" s="180"/>
+      <c r="E23" s="180"/>
+      <c r="F23" s="181"/>
       <c r="G23" s="16"/>
       <c r="H23" s="12">
         <v>5</v>
       </c>
-      <c r="I23" s="177"/>
-      <c r="J23" s="178"/>
-      <c r="K23" s="178"/>
-      <c r="L23" s="179"/>
+      <c r="I23" s="179"/>
+      <c r="J23" s="180"/>
+      <c r="K23" s="180"/>
+      <c r="L23" s="181"/>
     </row>
     <row r="24" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
@@ -4289,84 +4286,84 @@
       <c r="B24" s="14">
         <v>1</v>
       </c>
-      <c r="C24" s="135" t="s">
+      <c r="C24" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="137"/>
+      <c r="D24" s="168"/>
+      <c r="E24" s="168"/>
+      <c r="F24" s="169"/>
       <c r="G24" s="13" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="14">
         <v>1</v>
       </c>
-      <c r="I24" s="210" t="s">
+      <c r="I24" s="228" t="s">
         <v>99</v>
       </c>
-      <c r="J24" s="211"/>
-      <c r="K24" s="211"/>
-      <c r="L24" s="212"/>
+      <c r="J24" s="229"/>
+      <c r="K24" s="229"/>
+      <c r="L24" s="230"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="8"/>
       <c r="B25" s="15">
         <v>2</v>
       </c>
-      <c r="C25" s="156" t="s">
+      <c r="C25" s="120" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
-      <c r="F25" s="158"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="150"/>
       <c r="G25" s="8"/>
       <c r="H25" s="15">
         <v>2</v>
       </c>
-      <c r="I25" s="233" t="s">
+      <c r="I25" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="J25" s="234"/>
-      <c r="K25" s="235" t="s">
+      <c r="J25" s="232"/>
+      <c r="K25" s="233" t="s">
         <v>58</v>
       </c>
-      <c r="L25" s="236"/>
+      <c r="L25" s="234"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>
       <c r="B26" s="15">
         <v>3</v>
       </c>
-      <c r="C26" s="123" t="s">
+      <c r="C26" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="133"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="134"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="126"/>
       <c r="G26" s="8"/>
       <c r="H26" s="15">
         <v>3</v>
       </c>
-      <c r="I26" s="247" t="s">
+      <c r="I26" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="J26" s="248"/>
-      <c r="K26" s="248"/>
-      <c r="L26" s="249"/>
+      <c r="J26" s="213"/>
+      <c r="K26" s="213"/>
+      <c r="L26" s="214"/>
     </row>
     <row r="27" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16"/>
       <c r="B27" s="12"/>
-      <c r="C27" s="224"/>
-      <c r="D27" s="225"/>
-      <c r="E27" s="225"/>
-      <c r="F27" s="226"/>
+      <c r="C27" s="245"/>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="247"/>
       <c r="G27" s="16"/>
       <c r="H27" s="12"/>
-      <c r="I27" s="171"/>
-      <c r="J27" s="172"/>
-      <c r="K27" s="172"/>
-      <c r="L27" s="173"/>
+      <c r="I27" s="175"/>
+      <c r="J27" s="176"/>
+      <c r="K27" s="176"/>
+      <c r="L27" s="177"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="13" t="s">
@@ -4375,82 +4372,82 @@
       <c r="B28" s="14">
         <v>1</v>
       </c>
-      <c r="C28" s="180"/>
-      <c r="D28" s="181"/>
-      <c r="E28" s="181"/>
-      <c r="F28" s="182"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="144"/>
       <c r="G28" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="14">
         <v>1</v>
       </c>
-      <c r="I28" s="135" t="s">
+      <c r="I28" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="J28" s="136"/>
-      <c r="K28" s="136"/>
-      <c r="L28" s="137"/>
+      <c r="J28" s="168"/>
+      <c r="K28" s="168"/>
+      <c r="L28" s="169"/>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="18"/>
       <c r="B29" s="15">
         <v>2</v>
       </c>
-      <c r="C29" s="156" t="s">
-        <v>160</v>
-      </c>
-      <c r="D29" s="157"/>
-      <c r="E29" s="157"/>
-      <c r="F29" s="158"/>
+      <c r="C29" s="120" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="150"/>
       <c r="G29" s="8"/>
       <c r="H29" s="15">
         <v>2</v>
       </c>
-      <c r="I29" s="230"/>
-      <c r="J29" s="231"/>
-      <c r="K29" s="231"/>
-      <c r="L29" s="232"/>
+      <c r="I29" s="225"/>
+      <c r="J29" s="226"/>
+      <c r="K29" s="226"/>
+      <c r="L29" s="227"/>
     </row>
     <row r="30" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18"/>
       <c r="B30" s="15">
         <v>3</v>
       </c>
-      <c r="C30" s="156" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" s="157"/>
-      <c r="E30" s="157"/>
-      <c r="F30" s="158"/>
+      <c r="C30" s="120" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" s="121"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="150"/>
       <c r="G30" s="8"/>
       <c r="H30" s="15">
         <v>3</v>
       </c>
-      <c r="I30" s="250"/>
-      <c r="J30" s="251"/>
-      <c r="K30" s="251"/>
-      <c r="L30" s="252"/>
+      <c r="I30" s="216"/>
+      <c r="J30" s="217"/>
+      <c r="K30" s="217"/>
+      <c r="L30" s="218"/>
     </row>
     <row r="31" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19"/>
       <c r="B31" s="12">
         <v>4</v>
       </c>
-      <c r="C31" s="237" t="s">
-        <v>159</v>
-      </c>
-      <c r="D31" s="238"/>
-      <c r="E31" s="238"/>
-      <c r="F31" s="239"/>
+      <c r="C31" s="235" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="236"/>
+      <c r="E31" s="236"/>
+      <c r="F31" s="237"/>
       <c r="G31" s="16"/>
       <c r="H31" s="12">
         <v>4</v>
       </c>
-      <c r="I31" s="253"/>
-      <c r="J31" s="254"/>
-      <c r="K31" s="254"/>
-      <c r="L31" s="255"/>
+      <c r="I31" s="219"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="220"/>
+      <c r="L31" s="221"/>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
@@ -4459,124 +4456,124 @@
       <c r="B32" s="2">
         <v>1</v>
       </c>
-      <c r="C32" s="180" t="s">
-        <v>148</v>
-      </c>
-      <c r="D32" s="181"/>
-      <c r="E32" s="181"/>
-      <c r="F32" s="182"/>
+      <c r="C32" s="142" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="144"/>
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H32" s="14">
         <v>1</v>
       </c>
-      <c r="I32" s="135" t="s">
+      <c r="I32" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="J32" s="136"/>
-      <c r="K32" s="136"/>
-      <c r="L32" s="137"/>
+      <c r="J32" s="168"/>
+      <c r="K32" s="168"/>
+      <c r="L32" s="169"/>
     </row>
     <row r="33" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="26"/>
       <c r="B33" s="10">
         <v>2</v>
       </c>
-      <c r="C33" s="123" t="s">
-        <v>149</v>
-      </c>
-      <c r="D33" s="133"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="134"/>
+      <c r="C33" s="124" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="125"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="126"/>
       <c r="G33" s="23"/>
       <c r="H33" s="12">
         <v>2</v>
       </c>
-      <c r="I33" s="177"/>
-      <c r="J33" s="178"/>
-      <c r="K33" s="178"/>
-      <c r="L33" s="179"/>
+      <c r="I33" s="179"/>
+      <c r="J33" s="180"/>
+      <c r="K33" s="180"/>
+      <c r="L33" s="181"/>
     </row>
     <row r="34" spans="1:12" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="27"/>
       <c r="B34" s="24"/>
-      <c r="C34" s="227"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="228"/>
-      <c r="F34" s="229"/>
+      <c r="C34" s="248"/>
+      <c r="D34" s="249"/>
+      <c r="E34" s="249"/>
+      <c r="F34" s="250"/>
       <c r="G34" s="28"/>
       <c r="H34" s="29"/>
-      <c r="I34" s="256"/>
-      <c r="J34" s="257"/>
-      <c r="K34" s="257"/>
-      <c r="L34" s="258"/>
+      <c r="I34" s="222"/>
+      <c r="J34" s="223"/>
+      <c r="K34" s="223"/>
+      <c r="L34" s="224"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="99"/>
       <c r="B35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="180" t="s">
+      <c r="C35" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="181"/>
-      <c r="E35" s="181"/>
-      <c r="F35" s="182"/>
+      <c r="D35" s="143"/>
+      <c r="E35" s="143"/>
+      <c r="F35" s="144"/>
       <c r="G35" s="99"/>
       <c r="H35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="180" t="s">
+      <c r="I35" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="J35" s="181"/>
-      <c r="K35" s="181"/>
-      <c r="L35" s="182"/>
+      <c r="J35" s="143"/>
+      <c r="K35" s="143"/>
+      <c r="L35" s="144"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="100"/>
       <c r="B36" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="230" t="s">
+      <c r="C36" s="225" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="231"/>
-      <c r="E36" s="231"/>
-      <c r="F36" s="232"/>
+      <c r="D36" s="226"/>
+      <c r="E36" s="226"/>
+      <c r="F36" s="227"/>
       <c r="G36" s="100"/>
       <c r="H36" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I36" s="230" t="s">
+      <c r="I36" s="225" t="s">
         <v>67</v>
       </c>
-      <c r="J36" s="231"/>
-      <c r="K36" s="231"/>
-      <c r="L36" s="232"/>
+      <c r="J36" s="226"/>
+      <c r="K36" s="226"/>
+      <c r="L36" s="227"/>
     </row>
     <row r="37" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="101"/>
       <c r="B37" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="223" t="s">
+      <c r="C37" s="215" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="164"/>
-      <c r="E37" s="164"/>
-      <c r="F37" s="165"/>
+      <c r="D37" s="171"/>
+      <c r="E37" s="171"/>
+      <c r="F37" s="172"/>
       <c r="G37" s="101"/>
       <c r="H37" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="223" t="s">
+      <c r="I37" s="215" t="s">
         <v>66</v>
       </c>
-      <c r="J37" s="164"/>
-      <c r="K37" s="164"/>
-      <c r="L37" s="165"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
+      <c r="L37" s="172"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="35" t="s">
@@ -4608,13 +4605,43 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I16:L16"/>
     <mergeCell ref="I33:L33"/>
     <mergeCell ref="I35:L35"/>
     <mergeCell ref="I26:L26"/>
@@ -4631,43 +4658,13 @@
     <mergeCell ref="I24:L24"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C32:F32"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I17:L17"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 K5">
@@ -4892,20 +4889,20 @@
       <c r="A8" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="323" t="s">
+      <c r="C8" s="308" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="323"/>
-      <c r="E8" s="323"/>
+      <c r="D8" s="308"/>
+      <c r="E8" s="308"/>
       <c r="G8" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="325" t="s">
+      <c r="I8" s="280" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="325"/>
-      <c r="K8" s="325"/>
-      <c r="L8" s="325"/>
+      <c r="J8" s="280"/>
+      <c r="K8" s="280"/>
+      <c r="L8" s="280"/>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="75" t="s">
@@ -4940,86 +4937,86 @@
       <c r="B10" s="82">
         <v>2</v>
       </c>
-      <c r="C10" s="303" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="304"/>
-      <c r="E10" s="304"/>
-      <c r="F10" s="305"/>
+      <c r="C10" s="281" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="282"/>
+      <c r="E10" s="282"/>
+      <c r="F10" s="283"/>
       <c r="G10" s="81" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="82">
         <v>2</v>
       </c>
-      <c r="I10" s="329" t="s">
-        <v>118</v>
-      </c>
-      <c r="J10" s="330"/>
-      <c r="K10" s="330"/>
-      <c r="L10" s="331"/>
+      <c r="I10" s="287" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="288"/>
+      <c r="K10" s="288"/>
+      <c r="L10" s="289"/>
     </row>
     <row r="11" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="83"/>
       <c r="B11" s="84">
         <v>3</v>
       </c>
-      <c r="C11" s="320" t="s">
-        <v>117</v>
-      </c>
-      <c r="D11" s="321"/>
-      <c r="E11" s="321"/>
-      <c r="F11" s="322"/>
+      <c r="C11" s="305" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="306"/>
+      <c r="E11" s="306"/>
+      <c r="F11" s="307"/>
       <c r="G11" s="83"/>
       <c r="H11" s="84">
         <v>3</v>
       </c>
-      <c r="I11" s="332" t="s">
-        <v>119</v>
-      </c>
-      <c r="J11" s="333"/>
-      <c r="K11" s="333"/>
-      <c r="L11" s="334"/>
+      <c r="I11" s="290" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="291"/>
+      <c r="K11" s="291"/>
+      <c r="L11" s="292"/>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="83"/>
       <c r="B12" s="84">
         <v>4</v>
       </c>
-      <c r="C12" s="303" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="304"/>
-      <c r="E12" s="304"/>
-      <c r="F12" s="305"/>
+      <c r="C12" s="281" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="282"/>
+      <c r="E12" s="282"/>
+      <c r="F12" s="283"/>
       <c r="G12" s="83"/>
       <c r="H12" s="84">
         <v>4</v>
       </c>
-      <c r="I12" s="332" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" s="333"/>
-      <c r="K12" s="333"/>
-      <c r="L12" s="334"/>
+      <c r="I12" s="290" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="291"/>
+      <c r="K12" s="291"/>
+      <c r="L12" s="292"/>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="83"/>
       <c r="B13" s="84">
         <v>5</v>
       </c>
-      <c r="C13" s="310"/>
-      <c r="D13" s="311"/>
-      <c r="E13" s="311"/>
-      <c r="F13" s="312"/>
+      <c r="C13" s="309"/>
+      <c r="D13" s="310"/>
+      <c r="E13" s="310"/>
+      <c r="F13" s="311"/>
       <c r="G13" s="83"/>
       <c r="H13" s="84">
         <v>5</v>
       </c>
-      <c r="I13" s="335"/>
-      <c r="J13" s="336"/>
-      <c r="K13" s="336"/>
-      <c r="L13" s="337"/>
+      <c r="I13" s="293"/>
+      <c r="J13" s="294"/>
+      <c r="K13" s="294"/>
+      <c r="L13" s="295"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="85" t="s">
@@ -5028,88 +5025,88 @@
       <c r="B14" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="313" t="s">
+      <c r="C14" s="296" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="314"/>
-      <c r="E14" s="314"/>
-      <c r="F14" s="324"/>
+      <c r="D14" s="297"/>
+      <c r="E14" s="297"/>
+      <c r="F14" s="298"/>
       <c r="G14" s="85" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="313" t="s">
+      <c r="I14" s="296" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="314"/>
-      <c r="K14" s="314"/>
-      <c r="L14" s="324"/>
+      <c r="J14" s="297"/>
+      <c r="K14" s="297"/>
+      <c r="L14" s="298"/>
     </row>
     <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="83"/>
       <c r="B15" s="84">
         <v>6</v>
       </c>
-      <c r="C15" s="290"/>
-      <c r="D15" s="291"/>
-      <c r="E15" s="291"/>
-      <c r="F15" s="292"/>
+      <c r="C15" s="312"/>
+      <c r="D15" s="313"/>
+      <c r="E15" s="313"/>
+      <c r="F15" s="314"/>
       <c r="G15" s="83"/>
       <c r="H15" s="84">
         <v>4</v>
       </c>
-      <c r="I15" s="263" t="s">
-        <v>116</v>
-      </c>
-      <c r="J15" s="264"/>
-      <c r="K15" s="264"/>
-      <c r="L15" s="265"/>
+      <c r="I15" s="277" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="278"/>
+      <c r="K15" s="278"/>
+      <c r="L15" s="279"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="83"/>
       <c r="B16" s="84">
         <v>7</v>
       </c>
-      <c r="C16" s="303" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="304"/>
-      <c r="E16" s="304"/>
-      <c r="F16" s="305"/>
+      <c r="C16" s="281" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="282"/>
+      <c r="E16" s="282"/>
+      <c r="F16" s="283"/>
       <c r="G16" s="83"/>
       <c r="H16" s="84">
         <v>5</v>
       </c>
-      <c r="I16" s="263" t="s">
-        <v>133</v>
-      </c>
-      <c r="J16" s="264"/>
-      <c r="K16" s="264"/>
-      <c r="L16" s="265"/>
+      <c r="I16" s="277" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="278"/>
+      <c r="K16" s="278"/>
+      <c r="L16" s="279"/>
     </row>
     <row r="17" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="83"/>
       <c r="B17" s="84">
         <v>8</v>
       </c>
-      <c r="C17" s="266" t="s">
+      <c r="C17" s="319" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="267"/>
-      <c r="E17" s="267"/>
-      <c r="F17" s="268"/>
+      <c r="D17" s="320"/>
+      <c r="E17" s="320"/>
+      <c r="F17" s="321"/>
       <c r="G17" s="83"/>
       <c r="H17" s="84">
         <v>6</v>
       </c>
-      <c r="I17" s="338" t="s">
+      <c r="I17" s="299" t="s">
         <v>72</v>
       </c>
-      <c r="J17" s="339"/>
-      <c r="K17" s="339"/>
-      <c r="L17" s="340"/>
+      <c r="J17" s="300"/>
+      <c r="K17" s="300"/>
+      <c r="L17" s="301"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="85" t="s">
@@ -5118,84 +5115,84 @@
       <c r="B18" s="86">
         <v>2</v>
       </c>
-      <c r="C18" s="300" t="s">
-        <v>122</v>
-      </c>
-      <c r="D18" s="301"/>
-      <c r="E18" s="301"/>
-      <c r="F18" s="302"/>
+      <c r="C18" s="322" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="323"/>
+      <c r="E18" s="323"/>
+      <c r="F18" s="324"/>
       <c r="G18" s="85" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="86">
         <v>2</v>
       </c>
-      <c r="I18" s="135" t="s">
+      <c r="I18" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="J18" s="136"/>
-      <c r="K18" s="136"/>
-      <c r="L18" s="137"/>
+      <c r="J18" s="168"/>
+      <c r="K18" s="168"/>
+      <c r="L18" s="169"/>
     </row>
     <row r="19" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="83"/>
       <c r="B19" s="84">
         <v>3</v>
       </c>
-      <c r="C19" s="263" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="264"/>
-      <c r="E19" s="264"/>
-      <c r="F19" s="265"/>
+      <c r="C19" s="277" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="278"/>
+      <c r="E19" s="278"/>
+      <c r="F19" s="279"/>
       <c r="G19" s="83"/>
       <c r="H19" s="84">
         <v>3</v>
       </c>
-      <c r="I19" s="284"/>
-      <c r="J19" s="285"/>
-      <c r="K19" s="285"/>
-      <c r="L19" s="286"/>
+      <c r="I19" s="268"/>
+      <c r="J19" s="269"/>
+      <c r="K19" s="269"/>
+      <c r="L19" s="270"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="83"/>
       <c r="B20" s="84">
         <v>4</v>
       </c>
-      <c r="C20" s="303" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="304"/>
-      <c r="E20" s="304"/>
-      <c r="F20" s="305"/>
+      <c r="C20" s="281" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="282"/>
+      <c r="E20" s="282"/>
+      <c r="F20" s="283"/>
       <c r="G20" s="83"/>
       <c r="H20" s="84">
         <v>4</v>
       </c>
-      <c r="I20" s="284"/>
-      <c r="J20" s="285"/>
-      <c r="K20" s="285"/>
-      <c r="L20" s="286"/>
+      <c r="I20" s="268"/>
+      <c r="J20" s="269"/>
+      <c r="K20" s="269"/>
+      <c r="L20" s="270"/>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="87"/>
       <c r="B21" s="88">
         <v>5</v>
       </c>
-      <c r="C21" s="297" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="298"/>
-      <c r="E21" s="298"/>
-      <c r="F21" s="299"/>
+      <c r="C21" s="316" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="317"/>
+      <c r="E21" s="317"/>
+      <c r="F21" s="318"/>
       <c r="G21" s="87"/>
       <c r="H21" s="88">
         <v>5</v>
       </c>
-      <c r="I21" s="326"/>
-      <c r="J21" s="327"/>
-      <c r="K21" s="327"/>
-      <c r="L21" s="328"/>
+      <c r="I21" s="284"/>
+      <c r="J21" s="285"/>
+      <c r="K21" s="285"/>
+      <c r="L21" s="286"/>
     </row>
     <row r="22" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="85" t="s">
@@ -5204,90 +5201,90 @@
       <c r="B22" s="86">
         <v>2</v>
       </c>
-      <c r="C22" s="313" t="s">
+      <c r="C22" s="296" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="314"/>
-      <c r="E22" s="315"/>
-      <c r="F22" s="316"/>
+      <c r="D22" s="297"/>
+      <c r="E22" s="329"/>
+      <c r="F22" s="330"/>
       <c r="G22" s="85" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="86">
         <v>2</v>
       </c>
-      <c r="I22" s="313" t="s">
-        <v>126</v>
-      </c>
-      <c r="J22" s="314"/>
-      <c r="K22" s="314" t="s">
+      <c r="I22" s="296" t="s">
+        <v>125</v>
+      </c>
+      <c r="J22" s="297"/>
+      <c r="K22" s="297" t="s">
         <v>53</v>
       </c>
-      <c r="L22" s="324"/>
+      <c r="L22" s="298"/>
     </row>
     <row r="23" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="83"/>
       <c r="B23" s="84">
         <v>3</v>
       </c>
-      <c r="C23" s="320" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="321"/>
-      <c r="E23" s="321"/>
-      <c r="F23" s="322"/>
+      <c r="C23" s="305" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="306"/>
+      <c r="E23" s="306"/>
+      <c r="F23" s="307"/>
       <c r="G23" s="83"/>
       <c r="H23" s="84">
         <v>3</v>
       </c>
-      <c r="I23" s="317" t="s">
+      <c r="I23" s="302" t="s">
         <v>54</v>
       </c>
-      <c r="J23" s="318"/>
-      <c r="K23" s="318" t="s">
+      <c r="J23" s="303"/>
+      <c r="K23" s="303" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="319"/>
+      <c r="L23" s="304"/>
     </row>
     <row r="24" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="83"/>
       <c r="B24" s="84">
         <v>4</v>
       </c>
-      <c r="C24" s="290"/>
-      <c r="D24" s="296"/>
-      <c r="E24" s="309" t="s">
+      <c r="C24" s="312"/>
+      <c r="D24" s="315"/>
+      <c r="E24" s="328" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="305"/>
+      <c r="F24" s="283"/>
       <c r="G24" s="83"/>
       <c r="H24" s="84">
         <v>4</v>
       </c>
-      <c r="I24" s="263" t="s">
-        <v>128</v>
-      </c>
-      <c r="J24" s="264"/>
-      <c r="K24" s="264"/>
-      <c r="L24" s="265"/>
+      <c r="I24" s="277" t="s">
+        <v>127</v>
+      </c>
+      <c r="J24" s="278"/>
+      <c r="K24" s="278"/>
+      <c r="L24" s="279"/>
     </row>
     <row r="25" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="87"/>
       <c r="B25" s="88">
         <v>5</v>
       </c>
-      <c r="C25" s="310"/>
-      <c r="D25" s="311"/>
-      <c r="E25" s="311"/>
-      <c r="F25" s="312"/>
+      <c r="C25" s="309"/>
+      <c r="D25" s="310"/>
+      <c r="E25" s="310"/>
+      <c r="F25" s="311"/>
       <c r="G25" s="87"/>
       <c r="H25" s="88">
         <v>5</v>
       </c>
-      <c r="I25" s="341"/>
-      <c r="J25" s="342"/>
-      <c r="K25" s="342"/>
-      <c r="L25" s="343"/>
+      <c r="I25" s="262"/>
+      <c r="J25" s="263"/>
+      <c r="K25" s="263"/>
+      <c r="L25" s="264"/>
     </row>
     <row r="26" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="85" t="s">
@@ -5296,84 +5293,84 @@
       <c r="B26" s="86">
         <v>2</v>
       </c>
-      <c r="C26" s="306"/>
-      <c r="D26" s="307"/>
-      <c r="E26" s="307"/>
-      <c r="F26" s="308"/>
+      <c r="C26" s="325"/>
+      <c r="D26" s="326"/>
+      <c r="E26" s="326"/>
+      <c r="F26" s="327"/>
       <c r="G26" s="85" t="s">
         <v>25</v>
       </c>
       <c r="H26" s="86">
         <v>2</v>
       </c>
-      <c r="I26" s="344"/>
-      <c r="J26" s="345"/>
-      <c r="K26" s="345"/>
-      <c r="L26" s="346"/>
+      <c r="I26" s="265"/>
+      <c r="J26" s="266"/>
+      <c r="K26" s="266"/>
+      <c r="L26" s="267"/>
     </row>
     <row r="27" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="89"/>
       <c r="B27" s="84">
         <v>3</v>
       </c>
-      <c r="C27" s="303" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="304"/>
-      <c r="E27" s="304"/>
-      <c r="F27" s="305"/>
+      <c r="C27" s="281" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="282"/>
+      <c r="E27" s="282"/>
+      <c r="F27" s="283"/>
       <c r="G27" s="89"/>
       <c r="H27" s="84">
         <v>3</v>
       </c>
-      <c r="I27" s="284"/>
-      <c r="J27" s="285"/>
-      <c r="K27" s="285"/>
-      <c r="L27" s="286"/>
+      <c r="I27" s="268"/>
+      <c r="J27" s="269"/>
+      <c r="K27" s="269"/>
+      <c r="L27" s="270"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="104"/>
       <c r="B28" s="105">
         <v>4</v>
       </c>
-      <c r="C28" s="263" t="s">
+      <c r="C28" s="277" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="264"/>
-      <c r="E28" s="264"/>
-      <c r="F28" s="265"/>
+      <c r="D28" s="278"/>
+      <c r="E28" s="278"/>
+      <c r="F28" s="279"/>
       <c r="G28" s="104"/>
       <c r="H28" s="105">
         <v>4</v>
       </c>
-      <c r="I28" s="263" t="s">
+      <c r="I28" s="277" t="s">
         <v>75</v>
       </c>
-      <c r="J28" s="264"/>
-      <c r="K28" s="264"/>
-      <c r="L28" s="265"/>
+      <c r="J28" s="278"/>
+      <c r="K28" s="278"/>
+      <c r="L28" s="279"/>
     </row>
     <row r="29" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="90"/>
       <c r="B29" s="88">
         <v>5</v>
       </c>
-      <c r="C29" s="266" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="267"/>
-      <c r="E29" s="267"/>
-      <c r="F29" s="268"/>
+      <c r="C29" s="319" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="320"/>
+      <c r="E29" s="320"/>
+      <c r="F29" s="321"/>
       <c r="G29" s="90"/>
       <c r="H29" s="88">
         <v>5</v>
       </c>
-      <c r="I29" s="347" t="s">
-        <v>129</v>
-      </c>
-      <c r="J29" s="348"/>
-      <c r="K29" s="348"/>
-      <c r="L29" s="349"/>
+      <c r="I29" s="271" t="s">
+        <v>128</v>
+      </c>
+      <c r="J29" s="272"/>
+      <c r="K29" s="272"/>
+      <c r="L29" s="273"/>
     </row>
     <row r="30" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="91" t="s">
@@ -5382,138 +5379,138 @@
       <c r="B30" s="86">
         <v>1</v>
       </c>
-      <c r="C30" s="293" t="s">
+      <c r="C30" s="350" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="294"/>
-      <c r="E30" s="294"/>
-      <c r="F30" s="295"/>
+      <c r="D30" s="351"/>
+      <c r="E30" s="351"/>
+      <c r="F30" s="352"/>
       <c r="G30" s="91" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="86">
         <v>1</v>
       </c>
-      <c r="I30" s="350"/>
-      <c r="J30" s="351"/>
-      <c r="K30" s="351"/>
-      <c r="L30" s="352"/>
+      <c r="I30" s="274"/>
+      <c r="J30" s="275"/>
+      <c r="K30" s="275"/>
+      <c r="L30" s="276"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="92"/>
       <c r="B31" s="84">
         <v>2</v>
       </c>
-      <c r="C31" s="284"/>
-      <c r="D31" s="285"/>
-      <c r="E31" s="285"/>
-      <c r="F31" s="286"/>
+      <c r="C31" s="268"/>
+      <c r="D31" s="269"/>
+      <c r="E31" s="269"/>
+      <c r="F31" s="270"/>
       <c r="G31" s="92"/>
       <c r="H31" s="84">
         <v>2</v>
       </c>
-      <c r="I31" s="272" t="s">
+      <c r="I31" s="335" t="s">
         <v>76</v>
       </c>
-      <c r="J31" s="273"/>
-      <c r="K31" s="273"/>
-      <c r="L31" s="274"/>
+      <c r="J31" s="336"/>
+      <c r="K31" s="336"/>
+      <c r="L31" s="337"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="92"/>
       <c r="B32" s="84">
         <v>3</v>
       </c>
-      <c r="C32" s="290"/>
-      <c r="D32" s="291"/>
-      <c r="E32" s="291"/>
-      <c r="F32" s="292"/>
+      <c r="C32" s="312"/>
+      <c r="D32" s="313"/>
+      <c r="E32" s="313"/>
+      <c r="F32" s="314"/>
       <c r="G32" s="92"/>
       <c r="H32" s="84">
         <v>3</v>
       </c>
-      <c r="I32" s="287" t="s">
+      <c r="I32" s="347" t="s">
         <v>77</v>
       </c>
-      <c r="J32" s="288"/>
-      <c r="K32" s="288"/>
-      <c r="L32" s="289"/>
+      <c r="J32" s="348"/>
+      <c r="K32" s="348"/>
+      <c r="L32" s="349"/>
     </row>
     <row r="33" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="93"/>
       <c r="B33" s="88">
         <v>4</v>
       </c>
-      <c r="C33" s="281"/>
-      <c r="D33" s="282"/>
-      <c r="E33" s="282"/>
-      <c r="F33" s="283"/>
+      <c r="C33" s="344"/>
+      <c r="D33" s="345"/>
+      <c r="E33" s="345"/>
+      <c r="F33" s="346"/>
       <c r="G33" s="93"/>
       <c r="H33" s="88">
         <v>4</v>
       </c>
-      <c r="I33" s="278"/>
-      <c r="J33" s="279"/>
-      <c r="K33" s="279"/>
-      <c r="L33" s="280"/>
+      <c r="I33" s="341"/>
+      <c r="J33" s="342"/>
+      <c r="K33" s="342"/>
+      <c r="L33" s="343"/>
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="94"/>
       <c r="B34" s="95"/>
-      <c r="C34" s="275"/>
-      <c r="D34" s="276"/>
-      <c r="E34" s="276"/>
-      <c r="F34" s="277"/>
+      <c r="C34" s="338"/>
+      <c r="D34" s="339"/>
+      <c r="E34" s="339"/>
+      <c r="F34" s="340"/>
       <c r="G34" s="94"/>
       <c r="H34" s="95"/>
-      <c r="I34" s="275"/>
-      <c r="J34" s="276"/>
-      <c r="K34" s="276"/>
-      <c r="L34" s="277"/>
+      <c r="I34" s="338"/>
+      <c r="J34" s="339"/>
+      <c r="K34" s="339"/>
+      <c r="L34" s="340"/>
     </row>
     <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="96"/>
       <c r="B35" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="269" t="s">
+      <c r="C35" s="332" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="270"/>
-      <c r="E35" s="270"/>
-      <c r="F35" s="271"/>
+      <c r="D35" s="333"/>
+      <c r="E35" s="333"/>
+      <c r="F35" s="334"/>
       <c r="G35" s="96"/>
       <c r="H35" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="269" t="s">
+      <c r="I35" s="332" t="s">
         <v>52</v>
       </c>
-      <c r="J35" s="270"/>
-      <c r="K35" s="270"/>
-      <c r="L35" s="271"/>
+      <c r="J35" s="333"/>
+      <c r="K35" s="333"/>
+      <c r="L35" s="334"/>
     </row>
     <row r="36" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="102" t="s">
         <v>70</v>
       </c>
       <c r="B36" s="103"/>
-      <c r="C36" s="262" t="s">
+      <c r="C36" s="331" t="s">
         <v>71</v>
       </c>
-      <c r="D36" s="262"/>
-      <c r="E36" s="262"/>
-      <c r="F36" s="262"/>
+      <c r="D36" s="331"/>
+      <c r="E36" s="331"/>
+      <c r="F36" s="331"/>
       <c r="G36" s="102" t="s">
         <v>70</v>
       </c>
       <c r="H36" s="103"/>
-      <c r="I36" s="262" t="s">
+      <c r="I36" s="331" t="s">
         <v>71</v>
       </c>
-      <c r="J36" s="262"/>
-      <c r="K36" s="262"/>
-      <c r="L36" s="262"/>
+      <c r="J36" s="331"/>
+      <c r="K36" s="331"/>
+      <c r="L36" s="331"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="65" t="s">
@@ -5545,11 +5542,45 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="K22:L22"/>
     <mergeCell ref="I24:L24"/>
     <mergeCell ref="I8:L8"/>
     <mergeCell ref="C16:F16"/>
@@ -5566,45 +5597,11 @@
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="I16:L16"/>
     <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I30:L30"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="I6 C6"/>
@@ -5830,18 +5827,18 @@
       <c r="A9" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="368" t="s">
+      <c r="C9" s="375" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="368"/>
+      <c r="D9" s="375"/>
       <c r="E9" s="98"/>
       <c r="G9" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="368" t="s">
+      <c r="I9" s="375" t="s">
         <v>91</v>
       </c>
-      <c r="J9" s="368"/>
+      <c r="J9" s="375"/>
       <c r="K9" s="98"/>
     </row>
     <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
@@ -5877,80 +5874,80 @@
       <c r="B11" s="4">
         <v>2</v>
       </c>
-      <c r="C11" s="293" t="s">
+      <c r="C11" s="350" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="294"/>
-      <c r="E11" s="294"/>
-      <c r="F11" s="295"/>
+      <c r="D11" s="351"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="352"/>
       <c r="G11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="4">
         <v>1</v>
       </c>
-      <c r="I11" s="372"/>
-      <c r="J11" s="373"/>
-      <c r="K11" s="373"/>
-      <c r="L11" s="374"/>
+      <c r="I11" s="379"/>
+      <c r="J11" s="380"/>
+      <c r="K11" s="380"/>
+      <c r="L11" s="381"/>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="15">
         <v>3</v>
       </c>
-      <c r="C12" s="381"/>
-      <c r="D12" s="382"/>
-      <c r="E12" s="382"/>
-      <c r="F12" s="383"/>
+      <c r="C12" s="385"/>
+      <c r="D12" s="386"/>
+      <c r="E12" s="386"/>
+      <c r="F12" s="387"/>
       <c r="G12" s="8"/>
       <c r="H12" s="15">
         <v>2</v>
       </c>
-      <c r="I12" s="123"/>
-      <c r="J12" s="133"/>
-      <c r="K12" s="133"/>
-      <c r="L12" s="134"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="125"/>
+      <c r="L12" s="126"/>
     </row>
     <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
       <c r="B13" s="15">
         <v>4</v>
       </c>
-      <c r="C13" s="381"/>
-      <c r="D13" s="382"/>
-      <c r="E13" s="382"/>
-      <c r="F13" s="383"/>
+      <c r="C13" s="385"/>
+      <c r="D13" s="386"/>
+      <c r="E13" s="386"/>
+      <c r="F13" s="387"/>
       <c r="G13" s="8"/>
       <c r="H13" s="15">
         <v>3</v>
       </c>
-      <c r="I13" s="375" t="s">
-        <v>167</v>
-      </c>
-      <c r="J13" s="376"/>
-      <c r="K13" s="376"/>
-      <c r="L13" s="377"/>
+      <c r="I13" s="366" t="s">
+        <v>166</v>
+      </c>
+      <c r="J13" s="367"/>
+      <c r="K13" s="367"/>
+      <c r="L13" s="368"/>
     </row>
     <row r="14" spans="1:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="11"/>
       <c r="B14" s="12">
         <v>5</v>
       </c>
-      <c r="C14" s="384"/>
-      <c r="D14" s="385"/>
-      <c r="E14" s="385"/>
-      <c r="F14" s="386"/>
+      <c r="C14" s="388"/>
+      <c r="D14" s="389"/>
+      <c r="E14" s="389"/>
+      <c r="F14" s="390"/>
       <c r="G14" s="11"/>
       <c r="H14" s="12">
         <v>4</v>
       </c>
-      <c r="I14" s="163" t="s">
-        <v>140</v>
-      </c>
-      <c r="J14" s="166"/>
-      <c r="K14" s="166"/>
-      <c r="L14" s="167"/>
+      <c r="I14" s="170" t="s">
+        <v>139</v>
+      </c>
+      <c r="J14" s="173"/>
+      <c r="K14" s="173"/>
+      <c r="L14" s="174"/>
     </row>
     <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
@@ -5959,110 +5956,110 @@
       <c r="B15" s="14">
         <v>2</v>
       </c>
-      <c r="C15" s="378" t="s">
-        <v>136</v>
-      </c>
-      <c r="D15" s="379"/>
-      <c r="E15" s="379"/>
-      <c r="F15" s="380"/>
+      <c r="C15" s="382" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="383"/>
+      <c r="E15" s="383"/>
+      <c r="F15" s="384"/>
       <c r="G15" s="13" t="s">
         <v>22</v>
       </c>
       <c r="H15" s="14">
         <v>2</v>
       </c>
-      <c r="I15" s="369" t="s">
-        <v>147</v>
-      </c>
-      <c r="J15" s="370"/>
-      <c r="K15" s="370"/>
-      <c r="L15" s="371"/>
+      <c r="I15" s="376" t="s">
+        <v>145</v>
+      </c>
+      <c r="J15" s="377"/>
+      <c r="K15" s="377"/>
+      <c r="L15" s="378"/>
     </row>
     <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
       <c r="B16" s="15">
         <v>3</v>
       </c>
-      <c r="C16" s="353" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="354"/>
-      <c r="E16" s="354"/>
-      <c r="F16" s="355"/>
+      <c r="C16" s="400" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="401"/>
+      <c r="E16" s="401"/>
+      <c r="F16" s="402"/>
       <c r="G16" s="8"/>
       <c r="H16" s="15">
         <v>3</v>
       </c>
-      <c r="I16" s="197" t="s">
-        <v>147</v>
-      </c>
-      <c r="J16" s="216"/>
-      <c r="K16" s="216"/>
-      <c r="L16" s="200"/>
+      <c r="I16" s="162" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="208"/>
+      <c r="K16" s="208"/>
+      <c r="L16" s="165"/>
     </row>
     <row r="17" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
-      <c r="C17" s="240" t="s">
+      <c r="C17" s="238" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="241"/>
-      <c r="E17" s="157" t="s">
-        <v>132</v>
-      </c>
-      <c r="F17" s="158"/>
+      <c r="D17" s="239"/>
+      <c r="E17" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="F17" s="150"/>
       <c r="G17" s="8"/>
       <c r="H17" s="15">
         <v>4</v>
       </c>
-      <c r="I17" s="240" t="s">
-        <v>141</v>
-      </c>
-      <c r="J17" s="241"/>
-      <c r="K17" s="241"/>
-      <c r="L17" s="242"/>
+      <c r="I17" s="238" t="s">
+        <v>140</v>
+      </c>
+      <c r="J17" s="239"/>
+      <c r="K17" s="239"/>
+      <c r="L17" s="240"/>
     </row>
     <row r="18" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="15">
         <v>5</v>
       </c>
-      <c r="C18" s="156" t="s">
-        <v>131</v>
-      </c>
-      <c r="D18" s="157"/>
-      <c r="E18" s="241" t="s">
-        <v>138</v>
-      </c>
-      <c r="F18" s="242"/>
+      <c r="C18" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="121"/>
+      <c r="E18" s="239" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="240"/>
       <c r="G18" s="8"/>
       <c r="H18" s="15">
         <v>5</v>
       </c>
-      <c r="I18" s="123"/>
-      <c r="J18" s="133"/>
-      <c r="K18" s="133"/>
-      <c r="L18" s="134"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="126"/>
     </row>
     <row r="19" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16"/>
       <c r="B19" s="12">
         <v>6</v>
       </c>
-      <c r="C19" s="177"/>
-      <c r="D19" s="178"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="179"/>
+      <c r="C19" s="179"/>
+      <c r="D19" s="180"/>
+      <c r="E19" s="180"/>
+      <c r="F19" s="181"/>
       <c r="G19" s="16"/>
       <c r="H19" s="12">
         <v>6</v>
       </c>
-      <c r="I19" s="177"/>
-      <c r="J19" s="178"/>
-      <c r="K19" s="178"/>
-      <c r="L19" s="179"/>
+      <c r="I19" s="179"/>
+      <c r="J19" s="180"/>
+      <c r="K19" s="180"/>
+      <c r="L19" s="181"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
@@ -6071,104 +6068,104 @@
       <c r="B20" s="14">
         <v>4</v>
       </c>
-      <c r="C20" s="396"/>
-      <c r="D20" s="397"/>
-      <c r="E20" s="397"/>
-      <c r="F20" s="398"/>
+      <c r="C20" s="356"/>
+      <c r="D20" s="357"/>
+      <c r="E20" s="357"/>
+      <c r="F20" s="358"/>
       <c r="G20" s="13" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="14">
         <v>1</v>
       </c>
-      <c r="I20" s="399"/>
-      <c r="J20" s="400"/>
-      <c r="K20" s="401" t="s">
-        <v>138</v>
-      </c>
-      <c r="L20" s="402"/>
+      <c r="I20" s="359"/>
+      <c r="J20" s="360"/>
+      <c r="K20" s="361" t="s">
+        <v>137</v>
+      </c>
+      <c r="L20" s="362"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
       <c r="B21" s="15">
         <v>5</v>
       </c>
-      <c r="C21" s="138" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="139"/>
-      <c r="E21" s="139"/>
-      <c r="F21" s="140"/>
+      <c r="C21" s="157" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="149"/>
       <c r="G21" s="8"/>
       <c r="H21" s="15">
         <v>2</v>
       </c>
-      <c r="I21" s="123" t="s">
-        <v>142</v>
-      </c>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="134"/>
+      <c r="I21" s="124" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21" s="125"/>
+      <c r="K21" s="125"/>
+      <c r="L21" s="126"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8"/>
       <c r="B22" s="15">
         <v>6</v>
       </c>
-      <c r="C22" s="138" t="s">
-        <v>144</v>
-      </c>
-      <c r="D22" s="139"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="140"/>
+      <c r="C22" s="157" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="149"/>
       <c r="G22" s="8"/>
       <c r="H22" s="15">
         <v>3</v>
       </c>
-      <c r="I22" s="123" t="s">
-        <v>143</v>
-      </c>
-      <c r="J22" s="133"/>
-      <c r="K22" s="133"/>
-      <c r="L22" s="134"/>
+      <c r="I22" s="124" t="s">
+        <v>142</v>
+      </c>
+      <c r="J22" s="125"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="126"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8"/>
       <c r="B23" s="15">
         <v>7</v>
       </c>
-      <c r="C23" s="233" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="246"/>
-      <c r="E23" s="246"/>
-      <c r="F23" s="236"/>
+      <c r="C23" s="231" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="244"/>
+      <c r="E23" s="244"/>
+      <c r="F23" s="234"/>
       <c r="G23" s="8"/>
       <c r="H23" s="15">
         <v>4</v>
       </c>
-      <c r="I23" s="123"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="133"/>
-      <c r="L23" s="134"/>
+      <c r="I23" s="124"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="126"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16"/>
       <c r="B24" s="12">
         <v>8</v>
       </c>
-      <c r="C24" s="359"/>
-      <c r="D24" s="360"/>
-      <c r="E24" s="360"/>
-      <c r="F24" s="361"/>
+      <c r="C24" s="369"/>
+      <c r="D24" s="370"/>
+      <c r="E24" s="370"/>
+      <c r="F24" s="371"/>
       <c r="G24" s="16"/>
       <c r="H24" s="12">
         <v>5</v>
       </c>
-      <c r="I24" s="393"/>
-      <c r="J24" s="394"/>
-      <c r="K24" s="394"/>
-      <c r="L24" s="395"/>
+      <c r="I24" s="353"/>
+      <c r="J24" s="354"/>
+      <c r="K24" s="354"/>
+      <c r="L24" s="355"/>
     </row>
     <row r="25" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
@@ -6177,88 +6174,88 @@
       <c r="B25" s="14">
         <v>2</v>
       </c>
-      <c r="C25" s="135" t="s">
+      <c r="C25" s="167" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="136"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="137"/>
+      <c r="D25" s="168"/>
+      <c r="E25" s="168"/>
+      <c r="F25" s="169"/>
       <c r="G25" s="13" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="14">
         <v>1</v>
       </c>
-      <c r="I25" s="148" t="s">
-        <v>155</v>
-      </c>
-      <c r="J25" s="128"/>
-      <c r="K25" s="128"/>
-      <c r="L25" s="129"/>
+      <c r="I25" s="192" t="s">
+        <v>153</v>
+      </c>
+      <c r="J25" s="193"/>
+      <c r="K25" s="193"/>
+      <c r="L25" s="194"/>
     </row>
     <row r="26" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>
       <c r="B26" s="15">
         <v>3</v>
       </c>
-      <c r="C26" s="387" t="s">
-        <v>134</v>
-      </c>
-      <c r="D26" s="388"/>
-      <c r="E26" s="388"/>
-      <c r="F26" s="389"/>
+      <c r="C26" s="363" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" s="364"/>
+      <c r="E26" s="364"/>
+      <c r="F26" s="365"/>
       <c r="G26" s="8"/>
       <c r="H26" s="15">
         <v>2</v>
       </c>
-      <c r="I26" s="375" t="s">
-        <v>156</v>
-      </c>
-      <c r="J26" s="376"/>
-      <c r="K26" s="376"/>
-      <c r="L26" s="377"/>
+      <c r="I26" s="366" t="s">
+        <v>154</v>
+      </c>
+      <c r="J26" s="367"/>
+      <c r="K26" s="367"/>
+      <c r="L26" s="368"/>
     </row>
     <row r="27" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8"/>
       <c r="B27" s="15">
         <v>4</v>
       </c>
-      <c r="C27" s="233" t="s">
-        <v>135</v>
-      </c>
-      <c r="D27" s="246"/>
-      <c r="E27" s="246"/>
-      <c r="F27" s="236"/>
+      <c r="C27" s="231" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="244"/>
+      <c r="E27" s="244"/>
+      <c r="F27" s="234"/>
       <c r="G27" s="8"/>
       <c r="H27" s="15">
         <v>3</v>
       </c>
-      <c r="I27" s="390" t="s">
-        <v>139</v>
-      </c>
-      <c r="J27" s="391"/>
-      <c r="K27" s="391"/>
-      <c r="L27" s="392"/>
+      <c r="I27" s="372" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="373"/>
+      <c r="K27" s="373"/>
+      <c r="L27" s="374"/>
     </row>
     <row r="28" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16"/>
       <c r="B28" s="12">
         <v>5</v>
       </c>
-      <c r="C28" s="194" t="s">
+      <c r="C28" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="195"/>
-      <c r="E28" s="195"/>
-      <c r="F28" s="196"/>
+      <c r="D28" s="160"/>
+      <c r="E28" s="160"/>
+      <c r="F28" s="161"/>
       <c r="G28" s="16"/>
       <c r="H28" s="12">
         <v>4</v>
       </c>
-      <c r="I28" s="163"/>
-      <c r="J28" s="166"/>
-      <c r="K28" s="166"/>
-      <c r="L28" s="167"/>
+      <c r="I28" s="170"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="174"/>
     </row>
     <row r="29" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="13" t="s">
@@ -6267,88 +6264,88 @@
       <c r="B29" s="14">
         <v>1</v>
       </c>
-      <c r="C29" s="135" t="s">
-        <v>162</v>
-      </c>
-      <c r="D29" s="136"/>
-      <c r="E29" s="136"/>
-      <c r="F29" s="137"/>
+      <c r="C29" s="167" t="s">
+        <v>160</v>
+      </c>
+      <c r="D29" s="168"/>
+      <c r="E29" s="168"/>
+      <c r="F29" s="169"/>
       <c r="G29" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H29" s="14">
         <v>1</v>
       </c>
-      <c r="I29" s="293" t="s">
-        <v>153</v>
-      </c>
-      <c r="J29" s="294"/>
-      <c r="K29" s="294"/>
-      <c r="L29" s="295"/>
+      <c r="I29" s="350" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="351"/>
+      <c r="K29" s="351"/>
+      <c r="L29" s="352"/>
     </row>
     <row r="30" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18"/>
       <c r="B30" s="4">
         <v>2</v>
       </c>
-      <c r="C30" s="138" t="s">
-        <v>161</v>
-      </c>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="140"/>
+      <c r="C30" s="157" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="166"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="149"/>
       <c r="G30" s="18"/>
       <c r="H30" s="4">
         <v>2</v>
       </c>
-      <c r="I30" s="138" t="s">
-        <v>152</v>
-      </c>
-      <c r="J30" s="139"/>
-      <c r="K30" s="139"/>
-      <c r="L30" s="140"/>
+      <c r="I30" s="157" t="s">
+        <v>150</v>
+      </c>
+      <c r="J30" s="166"/>
+      <c r="K30" s="166"/>
+      <c r="L30" s="149"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="18"/>
       <c r="B31" s="15">
         <v>3</v>
       </c>
-      <c r="C31" s="138" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="140"/>
+      <c r="C31" s="157" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="166"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="149"/>
       <c r="G31" s="18"/>
       <c r="H31" s="15">
         <v>3</v>
       </c>
-      <c r="I31" s="365" t="s">
-        <v>154</v>
-      </c>
-      <c r="J31" s="366"/>
-      <c r="K31" s="366"/>
-      <c r="L31" s="367"/>
+      <c r="I31" s="391" t="s">
+        <v>152</v>
+      </c>
+      <c r="J31" s="392"/>
+      <c r="K31" s="392"/>
+      <c r="L31" s="393"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19"/>
       <c r="B32" s="12">
         <v>4</v>
       </c>
-      <c r="C32" s="194" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="195"/>
-      <c r="E32" s="195"/>
-      <c r="F32" s="196"/>
+      <c r="C32" s="159" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="160"/>
+      <c r="E32" s="160"/>
+      <c r="F32" s="161"/>
       <c r="G32" s="19"/>
       <c r="H32" s="12">
         <v>4</v>
       </c>
-      <c r="I32" s="356"/>
-      <c r="J32" s="357"/>
-      <c r="K32" s="357"/>
-      <c r="L32" s="358"/>
+      <c r="I32" s="394"/>
+      <c r="J32" s="395"/>
+      <c r="K32" s="395"/>
+      <c r="L32" s="396"/>
     </row>
     <row r="33" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20" t="s">
@@ -6357,96 +6354,96 @@
       <c r="B33" s="14">
         <v>1</v>
       </c>
-      <c r="C33" s="293" t="s">
+      <c r="C33" s="350" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="294"/>
-      <c r="E33" s="294"/>
-      <c r="F33" s="295"/>
+      <c r="D33" s="351"/>
+      <c r="E33" s="351"/>
+      <c r="F33" s="352"/>
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="14">
         <v>1</v>
       </c>
-      <c r="I33" s="183" t="s">
+      <c r="I33" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="J33" s="184"/>
-      <c r="K33" s="184"/>
-      <c r="L33" s="185"/>
+      <c r="J33" s="183"/>
+      <c r="K33" s="183"/>
+      <c r="L33" s="184"/>
     </row>
     <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="4">
         <v>2</v>
       </c>
-      <c r="C34" s="362"/>
-      <c r="D34" s="363"/>
-      <c r="E34" s="363"/>
-      <c r="F34" s="364"/>
+      <c r="C34" s="397"/>
+      <c r="D34" s="398"/>
+      <c r="E34" s="398"/>
+      <c r="F34" s="399"/>
       <c r="G34" s="21"/>
       <c r="H34" s="4">
         <v>2</v>
       </c>
-      <c r="I34" s="230" t="s">
+      <c r="I34" s="225" t="s">
         <v>57</v>
       </c>
-      <c r="J34" s="231"/>
-      <c r="K34" s="231"/>
-      <c r="L34" s="232"/>
+      <c r="J34" s="226"/>
+      <c r="K34" s="226"/>
+      <c r="L34" s="227"/>
     </row>
     <row r="35" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="15">
         <v>3</v>
       </c>
-      <c r="C35" s="362"/>
-      <c r="D35" s="363"/>
-      <c r="E35" s="363"/>
-      <c r="F35" s="364"/>
+      <c r="C35" s="397"/>
+      <c r="D35" s="398"/>
+      <c r="E35" s="398"/>
+      <c r="F35" s="399"/>
       <c r="G35" s="21"/>
       <c r="H35" s="15">
         <v>3</v>
       </c>
-      <c r="I35" s="230" t="s">
-        <v>151</v>
-      </c>
-      <c r="J35" s="231"/>
-      <c r="K35" s="231"/>
-      <c r="L35" s="232"/>
+      <c r="I35" s="225" t="s">
+        <v>149</v>
+      </c>
+      <c r="J35" s="226"/>
+      <c r="K35" s="226"/>
+      <c r="L35" s="227"/>
     </row>
     <row r="36" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="22"/>
       <c r="B36" s="17">
         <v>4</v>
       </c>
-      <c r="C36" s="362"/>
-      <c r="D36" s="363"/>
-      <c r="E36" s="363"/>
-      <c r="F36" s="364"/>
+      <c r="C36" s="397"/>
+      <c r="D36" s="398"/>
+      <c r="E36" s="398"/>
+      <c r="F36" s="399"/>
       <c r="G36" s="22"/>
       <c r="H36" s="17"/>
-      <c r="I36" s="362"/>
-      <c r="J36" s="363"/>
-      <c r="K36" s="363"/>
-      <c r="L36" s="364"/>
+      <c r="I36" s="397"/>
+      <c r="J36" s="398"/>
+      <c r="K36" s="398"/>
+      <c r="L36" s="399"/>
     </row>
     <row r="37" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="23"/>
       <c r="B37" s="12">
         <v>5</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="369"/>
+      <c r="D37" s="370"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="371"/>
       <c r="G37" s="23"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="171"/>
-      <c r="J37" s="172"/>
-      <c r="K37" s="172"/>
-      <c r="L37" s="173"/>
+      <c r="I37" s="175"/>
+      <c r="J37" s="176"/>
+      <c r="K37" s="176"/>
+      <c r="L37" s="177"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="35" t="s">
@@ -6478,27 +6475,33 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="I30:L30"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I15:L15"/>
@@ -6511,33 +6514,27 @@
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I25:L25"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 K5">
